--- a/data/kz/niches/niche_formats_GROCERY.xlsx
+++ b/data/kz/niches/niche_formats_GROCERY.xlsx
@@ -502,6 +502,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -590,12 +591,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -645,12 +646,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MEDIUM</t>
+          <t>GROCERY_STANDARD</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -700,12 +701,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_SPEC</t>
+          <t>GROCERY_PREMIUM</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -780,6 +781,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -835,12 +837,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -873,12 +875,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -911,12 +913,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -981,6 +983,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1031,12 +1034,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1064,12 +1067,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1132,6 +1135,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1231,6 +1235,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1545,6 +1550,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1670,6 +1676,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1750,12 +1757,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1809,12 +1816,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MEDIUM</t>
+          <t>GROCERY_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1868,12 +1875,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_SPEC</t>
+          <t>GROCERY_PREMIUM</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1973,6 +1980,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2093,12 +2101,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2168,12 +2176,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MEDIUM</t>
+          <t>GROCERY_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2243,12 +2251,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_SPEC</t>
+          <t>GROCERY_PREMIUM</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2354,6 +2362,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2424,12 +2433,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2471,12 +2480,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MEDIUM</t>
+          <t>GROCERY_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2514,12 +2523,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_SPEC</t>
+          <t>GROCERY_PREMIUM</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2593,6 +2602,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2663,12 +2673,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2708,12 +2718,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MEDIUM</t>
+          <t>GROCERY_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2753,12 +2763,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_SPEC</t>
+          <t>GROCERY_PREMIUM</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2831,6 +2841,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2886,12 +2897,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2928,12 +2939,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MEDIUM</t>
+          <t>GROCERY_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2970,12 +2981,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_SPEC</t>
+          <t>GROCERY_PREMIUM</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3048,6 +3059,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3118,12 +3130,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3179,12 +3191,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MEDIUM</t>
+          <t>GROCERY_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3240,12 +3252,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_SPEC</t>
+          <t>GROCERY_PREMIUM</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3332,6 +3344,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3377,12 +3390,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -3411,12 +3424,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -3445,12 +3458,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -3479,12 +3492,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -3540,6 +3553,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3565,12 +3579,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3587,12 +3601,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GROCERY_MINI</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
